--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,72 +417,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -2561,121 +2561,45 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BARRANQUILLA</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>PUERTA DORADA CRISTALINA</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-06</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BARRANQUILLA</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>AMARETTO</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>0</v>
@@ -2685,67 +2609,27 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BARRANQUILLA</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>RIVERBAY</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,11 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-03-25, 2026-03-31</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>0</v>
@@ -551,7 +555,11 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-03-24, 2026-03-25, 2026-03-31</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
@@ -615,19 +623,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -641,19 +649,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -671,7 +679,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-20, 2026-03-21, 2026-03-25, 2026-03-28, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -685,7 +693,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-20, 2026-03-21, 2026-03-24, 2026-03-25, 2026-03-28, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -751,19 +759,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-25</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -777,19 +785,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
         </is>
       </c>
       <c r="M8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="9">
@@ -815,19 +823,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-12, 2026-03-24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-24</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -841,15 +849,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
@@ -875,20 +887,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-05</t>
+          <t>2026-03-02, 2026-03-04, 2026-03-05, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>LUNES</t>
@@ -901,19 +913,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-04, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-30</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +943,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-09, 2026-03-16</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -945,7 +957,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-09</t>
+          <t>2026-03-06, 2026-03-09, 2026-03-18</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -977,13 +989,21 @@
           <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-19, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-19, 2026-03-27</t>
+        </is>
+      </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -997,19 +1017,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-27</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-27</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13">
@@ -1035,15 +1055,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>2026-03-03, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1057,15 +1081,19 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -1091,19 +1119,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05</t>
+          <t>2026-03-03, 2026-03-05, 2026-03-12, 2026-03-19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1117,19 +1145,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06</t>
+          <t>2026-03-03, 2026-03-06, 2026-03-13, 2026-03-26</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-13</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -1179,7 +1207,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-12, 2026-03-18, 2026-03-21</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1193,7 +1221,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-14, 2026-03-18</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1227,45 +1255,45 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-09</t>
+          <t>2026-03-04, 2026-03-09, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="18">
@@ -1291,45 +1319,45 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="19">
@@ -1355,15 +1383,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>2026-03-03, 2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1377,15 +1409,19 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>2026-03-05, 2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="20">
@@ -1433,7 +1469,11 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>0</v>
@@ -1445,7 +1485,7 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-16</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1479,41 +1519,45 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-15, 2026-03-24, 2026-03-30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-11</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-15, 2026-03-21, 2026-03-29, 2026-03-30</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="n">
+      <c r="N22" t="n">
         <v>0.25</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1603,19 +1647,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1629,19 +1673,19 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="M25" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="26">
@@ -1667,15 +1711,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-12, 2026-03-18, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1689,7 +1737,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-06</t>
+          <t>2026-03-04, 2026-03-06, 2026-03-12, 2026-03-18, 2026-03-31</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1719,7 +1767,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-20, 2026-03-24</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1733,7 +1781,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-20, 2026-03-24</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1765,13 +1813,21 @@
           <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1851,41 +1907,45 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-30</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-17, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-03-17, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="n">
+      <c r="N30" t="n">
         <v>0.5</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1943,20 +2003,20 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>JUEVES</t>
@@ -1969,19 +2029,19 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33">
@@ -2047,20 +2107,20 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05</t>
+          <t>2026-03-03, 2026-03-05, 2026-03-11, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
@@ -2073,19 +2133,19 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-15, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="35">
@@ -2111,20 +2171,20 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-18, 2026-03-26</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-18, 2026-03-26</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
         <v>1</v>
       </c>
-      <c r="H35" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>VIERNES</t>
@@ -2135,13 +2195,21 @@
           <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-13, 2026-03-20, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-03-13, 2026-03-20, 2026-03-28</t>
+        </is>
+      </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="36">
@@ -2159,7 +2227,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-17, 2026-03-18, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -2173,7 +2241,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-18, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2207,20 +2275,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
         <v>1</v>
       </c>
-      <c r="H37" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>JUEVES</t>
@@ -2233,19 +2301,19 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="M37" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" t="n">
         <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="38">
@@ -2303,15 +2371,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2325,19 +2397,19 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="M39" t="n">
+        <v>4</v>
+      </c>
+      <c r="N39" t="n">
         <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="40">
@@ -2363,20 +2435,20 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-14, 2026-03-19, 2026-03-28</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-14, 2026-03-19, 2026-03-28</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" t="n">
         <v>1</v>
       </c>
-      <c r="H40" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>VIERNES</t>
@@ -2389,19 +2461,19 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-18, 2026-03-20, 2026-03-28</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-20, 2026-03-28</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="41">
@@ -2427,20 +2499,20 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-19, 2026-03-27</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-19, 2026-03-27</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" t="n">
         <v>1</v>
       </c>
-      <c r="H41" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>VIERNES</t>
@@ -2453,19 +2525,19 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-19, 2026-03-27</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-27</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="42">
@@ -2521,11 +2593,7 @@
           <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>0</v>
@@ -2543,157 +2611,13 @@
           <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BUCARAMANGA</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>PARQUE ORIENTE SOLEIL</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>2</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11</t>
-        </is>
-      </c>
-      <c r="M47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -543,7 +543,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-25, 2026-03-31</t>
+          <t>2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -649,12 +649,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -679,7 +679,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-20, 2026-03-21, 2026-03-25, 2026-03-28, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-20, 2026-03-24, 2026-03-25, 2026-03-28, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -759,12 +759,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-25</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-25</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-26</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -785,12 +785,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -823,12 +823,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-12, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-26</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -849,12 +849,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-10, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-12, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -887,12 +887,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-05, 2026-03-12, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-02, 2026-03-04, 2026-03-07, 2026-03-13, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-07, 2026-03-13, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -943,7 +943,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-16</t>
+          <t>2026-03-09, 2026-03-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -957,7 +957,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-09, 2026-03-18</t>
+          <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -991,12 +991,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-03-12, 2026-03-19, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-13, 2026-03-27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-12, 2026-03-19, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-13, 2026-03-27</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1017,19 +1017,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-13, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-16, 2026-03-27</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-13, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-27</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1119,19 +1119,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05, 2026-03-12, 2026-03-19</t>
+          <t>2026-03-03, 2026-03-05, 2026-03-12, 2026-03-24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
+          <t>2026-03-05, 2026-03-12</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1145,19 +1145,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06, 2026-03-13, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-14</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -1207,7 +1207,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-12, 2026-03-18, 2026-03-21</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-12, 2026-03-18, 2026-03-22</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1255,45 +1255,45 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-09, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-13, 2026-03-21, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-03-13, 2026-03-21, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" t="n">
+      <c r="N17" t="n">
         <v>0.75</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1383,19 +1383,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1409,19 +1409,19 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-15, 2026-03-24, 2026-03-30</t>
+          <t>2026-03-05, 2026-03-15, 2026-03-21, 2026-03-29, 2026-03-30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-15, 2026-03-21, 2026-03-29, 2026-03-30</t>
+          <t>2026-03-10, 2026-03-15, 2026-03-21, 2026-03-29, 2026-03-30</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1737,19 +1737,19 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-06, 2026-03-12, 2026-03-18, 2026-03-31</t>
+          <t>2026-03-04, 2026-03-06, 2026-03-18, 2026-03-27</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-27</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
@@ -1813,21 +1813,13 @@
           <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1907,12 +1899,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-30</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-17, 2026-03-25, 2026-03-30</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1933,19 +1925,19 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-17, 2026-03-25</t>
+          <t>2026-03-02, 2026-03-10, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-17, 2026-03-25</t>
+          <t>2026-03-10, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31">
@@ -2107,19 +2099,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05, 2026-03-11, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-13, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-11, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2133,7 +2125,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-15, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-09, 2026-03-16, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2397,7 +2389,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-02, 2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2435,12 +2427,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-14, 2026-03-19, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-14, 2026-03-20, 2026-03-28</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-14, 2026-03-19, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-14, 2026-03-20, 2026-03-28</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2461,19 +2453,19 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-18, 2026-03-20, 2026-03-28</t>
+          <t>2026-03-07, 2026-03-18, 2026-03-20, 2026-03-30</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-20, 2026-03-28</t>
+          <t>2026-03-07, 2026-03-20</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -764,14 +764,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-26</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -828,14 +828,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-12, 2026-03-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -892,14 +892,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-13, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-13, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -996,14 +996,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-13, 2026-03-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1260,14 +1260,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-12</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1548,16 +1548,12 @@
           <t>2026-03-10, 2026-03-15, 2026-03-21, 2026-03-29, 2026-03-30</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2432,14 +2428,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-14, 2026-03-20, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-20</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
